--- a/links_lookup.xlsx
+++ b/links_lookup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Thesis_PC\Schleper Lab FACs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7342578-5484-4A11-92BB-36BD9E93AA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E400A31E-BD3B-4FEA-B5FA-18BE6B8B7D55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2550" yWindow="10130" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="10690" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="64">
   <si>
     <t>Batch.File</t>
   </si>
@@ -213,6 +213,18 @@
   </si>
   <si>
     <t>Batch_Analysis_05082026_B36.pdf</t>
+  </si>
+  <si>
+    <t>https://ucloud.univie.ac.at/index.php/f/1576432618</t>
+  </si>
+  <si>
+    <t>Batch_Analysis_14082026_B35.pdf</t>
+  </si>
+  <si>
+    <t>Batch_Analysis_14082026_B36.pdf</t>
+  </si>
+  <si>
+    <t>https://ucloud.univie.ac.at/index.php/f/1576432628</t>
   </si>
 </sst>
 </file>
@@ -600,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.75" bestFit="1" customWidth="1"/>
@@ -854,6 +866,22 @@
         <v>58</v>
       </c>
     </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
